--- a/anotacion/anotacion_A3.xlsx
+++ b/anotacion/anotacion_A3.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANOTACION" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -27,19 +26,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -51,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002A78D6"/>
+        <fgColor rgb="FF2A78D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEA"/>
+        <fgColor rgb="FFEFEFEA"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +91,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -451,12 +455,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.6" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Anotación de sentimiento · Analítica Educativa</t>
@@ -464,7 +468,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -474,7 +478,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -526,7 +530,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -557,7 +561,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -584,8 +588,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H251"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -658,7 +662,11 @@
           <t>Hombre culto.</t>
         </is>
       </c>
-      <c r="E2" s="7" t="n"/>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="n">
         <v>0</v>
       </c>
@@ -684,14 +692,18 @@
           <t>Bueno y cuidadoso.</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="7" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="28.8" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -710,7 +722,11 @@
           <t>No tiene capacidad para enseñar a los estudiantes. Siempre pierde el tiempo en clase.</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="n">
         <v>0</v>
       </c>
@@ -736,14 +752,18 @@
           <t>es el mejor</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="7" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="28.8" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -762,7 +782,11 @@
           <t>Es una buena profesora, pero debería desarrollar su técnica de enseñanza.</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="n">
         <v>0</v>
       </c>
@@ -788,14 +812,18 @@
           <t>No muy hábil como profesor.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="57.6" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -814,7 +842,11 @@
           <t>Su proceso de enseñanza es muy bueno para que el estudiante pueda entender. Es muy inteligente, lo que se refleja en el estudiante. Siempre se preocupa por los estudiantes. Tiene muchas ideas sobre toda la materia, lo cual es muy agradable.</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
@@ -840,11 +872,19 @@
           <t>Es un muy buen profesor, pero nos estresa mucho.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H9" s="7" t="n"/>
     </row>
     <row r="10">
@@ -866,7 +906,11 @@
           <t>Es una profesora muy agradable. Estamos aprendiendo algo de ella.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
       </c>
@@ -892,14 +936,18 @@
           <t>Ayuda a entender la materia y a hacerla más fácil de comprender.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="28.8" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -918,11 +966,19 @@
           <t>es un buen profesor pero su nivel de enseñanza es demasiado alto para mí.</t>
         </is>
       </c>
-      <c r="E12" s="7" t="n"/>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
@@ -944,14 +1000,18 @@
           <t>Me cae muy bien. Siempre se preocupa por mí. Es muy amable.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="43.2" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -970,11 +1030,19 @@
           <t>No conozco a este profesor, ¿quién es? Mi profesor de tesis es Moinul, pero aparece Jahidul. Estoy muy confundido con esto. Completé mi TBI hace muchos días.</t>
         </is>
       </c>
-      <c r="E14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
@@ -996,7 +1064,11 @@
           <t>Profesor respetable.</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="n">
         <v>0</v>
       </c>
@@ -1022,14 +1094,18 @@
           <t>Es una gran profesora, una buena profesora.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="57.6" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1048,7 +1124,11 @@
           <t>No puede impartir bien las ensenanzas y, cuando se le pide que repita un tema, se burla e insulta a los estudiantes en lugar de explicar el tema con mas claridad. Esto hace la materia aun mas dificil de lo que es y tambien hace que estudiarla sea molesto.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F17" s="7" t="n">
         <v>0</v>
       </c>
@@ -1074,7 +1154,11 @@
           <t>¡Es realmente bueno!</t>
         </is>
       </c>
-      <c r="E18" s="7" t="n"/>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F18" s="7" t="n">
         <v>0</v>
       </c>
@@ -1100,14 +1184,18 @@
           <t>Es buena, pero debería ser más moderada al poner notas.</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="43.2" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1126,14 +1214,22 @@
           <t>Esta materia se ha vuelto un pánico para nosotros por las malas notas. Deberían darnos algunos puntos extra. Nos será muy difícil continuar con esta nota. También sería muy doloroso perder puntos en esta materia.</t>
         </is>
       </c>
-      <c r="E20" s="7" t="n"/>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="28.8" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1152,7 +1248,11 @@
           <t>Es bueno. Tiene algo en su actitud que realmente ayuda al estudiante a mantenerse en clase. Buen profesor.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F21" s="7" t="n">
         <v>0</v>
       </c>
@@ -1178,14 +1278,22 @@
           <t>Es un buen profesor, pero habla muy rápido.</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n"/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="28.8" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1204,11 +1312,19 @@
           <t>Es un muy buen profesor, pero debe mejorar su inglés hablado para nosotros (estudiantes de medio inglés).</t>
         </is>
       </c>
-      <c r="E23" s="7" t="n"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
@@ -1230,14 +1346,18 @@
           <t>El profesor más equilibrado que he visto</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n"/>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="7" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="28.8" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1256,14 +1376,18 @@
           <t>No tiene suficiente confianza. Creo que debería capacitarse mejor. A veces confunde su material de enseñanza.</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n"/>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="43.2" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1282,11 +1406,19 @@
           <t>Su conocimiento sobre este tema es bueno. Pero a veces no entendemos. El 50% de los estudiantes viene del departamento de ciencias. Es difícil de entender.</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
@@ -1308,7 +1440,11 @@
           <t>Es un profesor bueno y responsable.</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n"/>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F27" s="7" t="n">
         <v>0</v>
       </c>
@@ -1334,7 +1470,11 @@
           <t>Es un gran profesor.</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n"/>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
       </c>
@@ -1360,7 +1500,11 @@
           <t>Es una profesora eficiente</t>
         </is>
       </c>
-      <c r="E29" s="7" t="n"/>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
       </c>
@@ -1386,7 +1530,11 @@
           <t>Esta entre el punado de buenos profesores de EEE.</t>
         </is>
       </c>
-      <c r="E30" s="7" t="n"/>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F30" s="7" t="n">
         <v>0</v>
       </c>
@@ -1412,14 +1560,18 @@
           <t>Desempeño sobresaliente.</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="28.8" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1438,11 +1590,19 @@
           <t>La situación actual es buena para nosotros; si AIUB organizara un curso básico de inglés para los estudiantes, nos sería aún más útil.</t>
         </is>
       </c>
-      <c r="E32" s="7" t="n"/>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H32" s="7" t="n"/>
     </row>
     <row r="33">
@@ -1464,7 +1624,11 @@
           <t>Es un profesor agradable.</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="n">
         <v>0</v>
       </c>
@@ -1490,7 +1654,11 @@
           <t>Sabe todo sobre la materia, pero no puede enseñarnos adecuadamente.</t>
         </is>
       </c>
-      <c r="E34" s="7" t="n"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F34" s="7" t="n">
         <v>0</v>
       </c>
@@ -1516,11 +1684,19 @@
           <t>una tontería.</t>
         </is>
       </c>
-      <c r="E35" s="7" t="n"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H35" s="7" t="n"/>
     </row>
     <row r="36">
@@ -1542,7 +1718,11 @@
           <t>Es bueno.</t>
         </is>
       </c>
-      <c r="E36" s="7" t="n"/>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F36" s="7" t="n">
         <v>0</v>
       </c>
@@ -1568,7 +1748,11 @@
           <t>El mejor</t>
         </is>
       </c>
-      <c r="E37" s="7" t="n"/>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="n">
         <v>0</v>
       </c>
@@ -1594,7 +1778,11 @@
           <t>Es una muy buena profesora.</t>
         </is>
       </c>
-      <c r="E38" s="7" t="n"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
       </c>
@@ -1620,14 +1808,18 @@
           <t>Buen profesor.</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F39" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="7" t="n"/>
     </row>
-    <row r="40">
+    <row r="40" ht="28.8" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1646,14 +1838,18 @@
           <t>Nunca ve las cosas desde la perspectiva del estudiante. No sabe enseñar aunque sabe mucho.</t>
         </is>
       </c>
-      <c r="E40" s="7" t="n"/>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="7" t="n"/>
     </row>
-    <row r="41">
+    <row r="41" ht="28.8" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1672,14 +1868,18 @@
           <t>No entendemos lo que nos quiere enseñar. Tarda mucho tiempo en hacer entender cualquier cosa.</t>
         </is>
       </c>
-      <c r="E41" s="7" t="n"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="7" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="28.8" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1698,11 +1898,19 @@
           <t>Es un profesor muy agradable, pero es muy duro con el sistema de calificación.</t>
         </is>
       </c>
-      <c r="E42" s="7" t="n"/>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
@@ -1724,7 +1932,11 @@
           <t>El mejor profesor</t>
         </is>
       </c>
-      <c r="E43" s="7" t="n"/>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F43" s="7" t="n">
         <v>0</v>
       </c>
@@ -1750,7 +1962,11 @@
           <t>Su cara agradable y alegre es notable. Buen profesor.</t>
         </is>
       </c>
-      <c r="E44" s="7" t="n"/>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F44" s="7" t="n">
         <v>0</v>
       </c>
@@ -1776,7 +1992,11 @@
           <t>Es perfecto como profesor</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F45" s="7" t="n">
         <v>0</v>
       </c>
@@ -1802,7 +2022,11 @@
           <t>Realmente es un buen profesor.</t>
         </is>
       </c>
-      <c r="E46" s="7" t="n"/>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F46" s="7" t="n">
         <v>0</v>
       </c>
@@ -1828,7 +2052,11 @@
           <t>Realmente malo</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F47" s="7" t="n">
         <v>0</v>
       </c>
@@ -1854,7 +2082,11 @@
           <t>Excelentes habilidades.</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F48" s="7" t="n">
         <v>0</v>
       </c>
@@ -1880,7 +2112,11 @@
           <t>Es una buena profesora.</t>
         </is>
       </c>
-      <c r="E49" s="7" t="n"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F49" s="7" t="n">
         <v>0</v>
       </c>
@@ -1906,7 +2142,11 @@
           <t>Es muy bueno</t>
         </is>
       </c>
-      <c r="E50" s="7" t="n"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F50" s="7" t="n">
         <v>0</v>
       </c>
@@ -1932,7 +2172,11 @@
           <t>es muy agradable y todos disfrutamos su clase.</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F51" s="7" t="n">
         <v>0</v>
       </c>
@@ -1958,14 +2202,22 @@
           <t>no dio puntos parciales</t>
         </is>
       </c>
-      <c r="E52" s="7" t="n"/>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H52" s="7" t="n"/>
     </row>
-    <row r="53">
+    <row r="53" ht="28.8" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -1984,11 +2236,19 @@
           <t>es muy servicial y amigable, pero en la clase de laboratorio va muy rápido. si diera más tiempo a cada tema sería más útil</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54">
@@ -2010,7 +2270,11 @@
           <t>nos hace entender la materia muy claramente.</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F54" s="7" t="n">
         <v>0</v>
       </c>
@@ -2036,7 +2300,11 @@
           <t>El profesor es simplemente el mejor.</t>
         </is>
       </c>
-      <c r="E55" s="7" t="n"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F55" s="7" t="n">
         <v>0</v>
       </c>
@@ -2062,14 +2330,18 @@
           <t>Es el profesor más cariñoso.</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n"/>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="28.8" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2088,11 +2360,19 @@
           <t>muy buen profesor. pero nunca sonríe en clase. queremos ver su cara sonriente.</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H57" s="7" t="n"/>
     </row>
     <row r="58">
@@ -2114,14 +2394,18 @@
           <t>Responsable.</t>
         </is>
       </c>
-      <c r="E58" s="7" t="n"/>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="28.8" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2140,14 +2424,18 @@
           <t>gracias! esperaba tenerlo como profesor en algun curso. finalmente tuve la oportunidad de tener clase con usted.</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n"/>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="7" t="n"/>
       <c r="H59" s="7" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="57.6" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2166,7 +2454,11 @@
           <t>Aunque no soy uno de los estudiantes de su primer lote del primer semestre, por eso puedo dar un 100% de garantía de que es uno de los mejores profesores que he visto en toda mi vida universitaria. Mucha suerte, profesor.</t>
         </is>
       </c>
-      <c r="E60" s="7" t="n"/>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F60" s="7" t="n">
         <v>0</v>
       </c>
@@ -2192,7 +2484,11 @@
           <t>No tan bueno. Él entiende todo, pero no se lo transmite al estudiante.</t>
         </is>
       </c>
-      <c r="E61" s="7" t="n"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F61" s="7" t="n">
         <v>0</v>
       </c>
@@ -2218,7 +2514,11 @@
           <t>es un profesor muy guapo y agradable en aiub.</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F62" s="7" t="n">
         <v>0</v>
       </c>
@@ -2244,7 +2544,11 @@
           <t>Es una profesora agradable, además de muy estricta y amable.</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F63" s="7" t="n">
         <v>0</v>
       </c>
@@ -2270,14 +2574,18 @@
           <t>Muy bueno.</t>
         </is>
       </c>
-      <c r="E64" s="7" t="n"/>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F64" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="7" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="43.2" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2296,11 +2604,19 @@
           <t>Es un buen profesor. Debería explicar los experimentos de laboratorio, sus procedimientos y resultados de forma más detallada a los estudiantes.</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n"/>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H65" s="7" t="n"/>
     </row>
     <row r="66">
@@ -2322,14 +2638,18 @@
           <t>Buenos modales.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n"/>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F66" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
     </row>
-    <row r="67">
+    <row r="67" ht="43.2" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2348,7 +2668,11 @@
           <t>Un profesor que trata de preparar a los estudiantes para enfrentar la vida practica o profesional de forma independiente. Gracias tanto al profesor como a la administracion de la universidad.</t>
         </is>
       </c>
-      <c r="E67" s="7" t="n"/>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F67" s="7" t="n">
         <v>0</v>
       </c>
@@ -2374,7 +2698,11 @@
           <t>Es un buen profesor. Le deseo suerte.</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n"/>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F68" s="7" t="n">
         <v>0</v>
       </c>
@@ -2400,11 +2728,19 @@
           <t>Sin comentarios.</t>
         </is>
       </c>
-      <c r="E69" s="7" t="n"/>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="n"/>
     </row>
     <row r="70">
@@ -2426,7 +2762,11 @@
           <t>No es idóneo como docente de este curso.</t>
         </is>
       </c>
-      <c r="E70" s="7" t="n"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F70" s="7" t="n">
         <v>0</v>
       </c>
@@ -2452,7 +2792,11 @@
           <t>No es un buen profesor.</t>
         </is>
       </c>
-      <c r="E71" s="7" t="n"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F71" s="7" t="n">
         <v>0</v>
       </c>
@@ -2478,7 +2822,11 @@
           <t>gracias</t>
         </is>
       </c>
-      <c r="E72" s="7" t="n"/>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F72" s="7" t="n">
         <v>0</v>
       </c>
@@ -2504,7 +2852,11 @@
           <t>Profesor excelente</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F73" s="7" t="n">
         <v>0</v>
       </c>
@@ -2530,11 +2882,19 @@
           <t>el tema es subjetivo, sin embargo podria hacerse mas interesante.</t>
         </is>
       </c>
-      <c r="E74" s="7" t="n"/>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F74" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="n"/>
     </row>
     <row r="75">
@@ -2556,7 +2916,11 @@
           <t>Profesor respetable.</t>
         </is>
       </c>
-      <c r="E75" s="7" t="n"/>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F75" s="7" t="n">
         <v>0</v>
       </c>
@@ -2582,7 +2946,11 @@
           <t>Mantiene un buen y adecuado horario de clases.</t>
         </is>
       </c>
-      <c r="E76" s="7" t="n"/>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F76" s="7" t="n">
         <v>0</v>
       </c>
@@ -2608,14 +2976,18 @@
           <t>Necesita saber cómo enseñar a los estudiantes.</t>
         </is>
       </c>
-      <c r="E77" s="7" t="n"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F77" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
     </row>
-    <row r="78">
+    <row r="78" ht="28.8" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2634,7 +3006,11 @@
           <t>Es bueno pero a veces su actitud se vuelve irritante, especialmente con los horarios de sus clases de recuperación o adicionales.</t>
         </is>
       </c>
-      <c r="E78" s="7" t="n"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F78" s="7" t="n">
         <v>0</v>
       </c>
@@ -2660,14 +3036,22 @@
           <t>Muy buen profesor, pero deberia haber ensenado mas sobre la materia.</t>
         </is>
       </c>
-      <c r="E79" s="7" t="n"/>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F79" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H79" s="7" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="57.6" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2686,7 +3070,11 @@
           <t>Es una de las mejores profesoras de aiub. Ha mejorado mucho respecto al pasado. Su estilo de enseñanza, su política de exámenes y su comportamiento son simplemente buenos. Debería continuar así. Aprendemos algo de ella.</t>
         </is>
       </c>
-      <c r="E80" s="7" t="n"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F80" s="7" t="n">
         <v>0</v>
       </c>
@@ -2712,7 +3100,11 @@
           <t>Excelente</t>
         </is>
       </c>
-      <c r="E81" s="7" t="n"/>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F81" s="7" t="n">
         <v>0</v>
       </c>
@@ -2738,11 +3130,19 @@
           <t>Nada.</t>
         </is>
       </c>
-      <c r="E82" s="7" t="n"/>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F82" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H82" s="7" t="n"/>
     </row>
     <row r="83">
@@ -2764,7 +3164,11 @@
           <t>El profesor más equilibrado que he visto</t>
         </is>
       </c>
-      <c r="E83" s="7" t="n"/>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F83" s="7" t="n">
         <v>0</v>
       </c>
@@ -2790,11 +3194,19 @@
           <t>Bueno. Pero debería dar buenas notas cuando las merecemos</t>
         </is>
       </c>
-      <c r="E84" s="7" t="n"/>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F84" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H84" s="7" t="n"/>
     </row>
     <row r="85">
@@ -2816,11 +3228,19 @@
           <t>mejorate a ti mismo</t>
         </is>
       </c>
-      <c r="E85" s="7" t="n"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H85" s="7" t="n"/>
     </row>
     <row r="86">
@@ -2842,14 +3262,18 @@
           <t>En general, es un buen profesor.</t>
         </is>
       </c>
-      <c r="E86" s="7" t="n"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F86" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="7" t="n"/>
     </row>
-    <row r="87">
+    <row r="87" ht="100.8" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2868,7 +3292,11 @@
           <t>No es para nada un buen profesor. Su comportamiento también es muy malo. Necesitamos cambiar a este profesor para mejorar la educación en AIUB. Los estudiantes no aprenden nada de él. No tiene una idea clara de su materia. Si le preguntas algo sobre la materia, dice: "Intenta resolverlo tú mismo. No vengo aquí a resolver tus problemas". Siempre se confunde cuando nos enseña algo. Le pido a la rectora que lo cambie lo antes posible.</t>
         </is>
       </c>
-      <c r="E87" s="7" t="n"/>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F87" s="7" t="n">
         <v>0</v>
       </c>
@@ -2894,14 +3322,22 @@
           <t>no da puntos parciales</t>
         </is>
       </c>
-      <c r="E88" s="7" t="n"/>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F88" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H88" s="7" t="n"/>
     </row>
-    <row r="89">
+    <row r="89" ht="28.8" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2920,14 +3356,18 @@
           <t>Es muy buen profesor y se asegura de que el estudiante haya entendido bien su lección.</t>
         </is>
       </c>
-      <c r="E89" s="7" t="n"/>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
     </row>
-    <row r="90">
+    <row r="90" ht="28.8" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2946,14 +3386,18 @@
           <t>Enseña su lección de forma muy comprensible y es muy efectivo para el estudiante.</t>
         </is>
       </c>
-      <c r="E90" s="7" t="n"/>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F90" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="7" t="n"/>
     </row>
-    <row r="91">
+    <row r="91" ht="43.2" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -2972,7 +3416,11 @@
           <t>si hablo con honestidad, es un profesor realmente bueno para los conceptos de contabilidad; es cierto que tuvimos la mala suerte de no tenerlo desde el comienzo de este curso.</t>
         </is>
       </c>
-      <c r="E91" s="7" t="n"/>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F91" s="7" t="n">
         <v>0</v>
       </c>
@@ -2998,14 +3446,22 @@
           <t>Es una muy buena profesora, pero es muy débil en inglés.</t>
         </is>
       </c>
-      <c r="E92" s="7" t="n"/>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F92" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H92" s="7" t="n"/>
     </row>
-    <row r="93">
+    <row r="93" ht="28.8" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3024,11 +3480,19 @@
           <t>Es un buen tipo, pero hay un problema con el. A veces agranda mucho las cosas pequeñas. Aun asi, es un muy buen profesor.</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n"/>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F93" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H93" s="7" t="n"/>
     </row>
     <row r="94">
@@ -3050,11 +3514,19 @@
           <t>una tontería.</t>
         </is>
       </c>
-      <c r="E94" s="7" t="n"/>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F94" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H94" s="7" t="n"/>
     </row>
     <row r="95">
@@ -3076,7 +3548,11 @@
           <t>mmm, es un buen profesor. Me gusta su enseñanza. :-)</t>
         </is>
       </c>
-      <c r="E95" s="7" t="n"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F95" s="7" t="n">
         <v>0</v>
       </c>
@@ -3102,14 +3578,18 @@
           <t>Debería ser más comprensible.</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n"/>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F96" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="28.8" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3128,7 +3608,11 @@
           <t>Tiene una personalidad agradable. Explica las cosas de una manera muy loable.</t>
         </is>
       </c>
-      <c r="E97" s="7" t="n"/>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F97" s="7" t="n">
         <v>0</v>
       </c>
@@ -3154,7 +3638,11 @@
           <t>Bueno.</t>
         </is>
       </c>
-      <c r="E98" s="7" t="n"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F98" s="7" t="n">
         <v>0</v>
       </c>
@@ -3180,11 +3668,19 @@
           <t>Ninguno.</t>
         </is>
       </c>
-      <c r="E99" s="7" t="n"/>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F99" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H99" s="7" t="n"/>
     </row>
     <row r="100">
@@ -3206,7 +3702,11 @@
           <t>Es un buen profesor. Sabe enseñar derecho comercial.</t>
         </is>
       </c>
-      <c r="E100" s="7" t="n"/>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F100" s="7" t="n">
         <v>0</v>
       </c>
@@ -3232,14 +3732,22 @@
           <t>Bien.</t>
         </is>
       </c>
-      <c r="E101" s="7" t="n"/>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H101" s="7" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="28.8" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3258,14 +3766,22 @@
           <t>Un profesor muy bueno y comprensivo. Pero seria muy util si diera la clase en ingles.</t>
         </is>
       </c>
-      <c r="E102" s="7" t="n"/>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H102" s="7" t="n"/>
     </row>
-    <row r="103">
+    <row r="103" ht="28.8" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3284,11 +3800,19 @@
           <t>creo que es una buena profesora. hace todo lo posible para que las lecciones nos queden claras. pero a la mayoría de nosotros no.</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n"/>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H103" s="7" t="n"/>
     </row>
     <row r="104">
@@ -3310,7 +3834,11 @@
           <t>Es uno de los mejores profesores de aiub.</t>
         </is>
       </c>
-      <c r="E104" s="7" t="n"/>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F104" s="7" t="n">
         <v>0</v>
       </c>
@@ -3336,14 +3864,22 @@
           <t>No está mal, pero tampoco tan bueno.</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n"/>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H105" s="7" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="28.8" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3362,11 +3898,19 @@
           <t>Nuestro respetable profesor. Habla bastante rápido, con énfasis, de modo que a veces no entendemos lo que quiere decir. Es bueno.</t>
         </is>
       </c>
-      <c r="E106" s="7" t="n"/>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F106" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H106" s="7" t="n"/>
     </row>
     <row r="107">
@@ -3388,11 +3932,19 @@
           <t>Debería dar puntos extra.</t>
         </is>
       </c>
-      <c r="E107" s="7" t="n"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F107" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H107" s="7" t="n"/>
     </row>
     <row r="108">
@@ -3414,7 +3966,11 @@
           <t>Es muy buen profesor para esta materia</t>
         </is>
       </c>
-      <c r="E108" s="7" t="n"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F108" s="7" t="n">
         <v>0</v>
       </c>
@@ -3440,11 +3996,19 @@
           <t>Está dibujando.</t>
         </is>
       </c>
-      <c r="E109" s="7" t="n"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H109" s="7" t="n"/>
     </row>
     <row r="110">
@@ -3466,14 +4030,18 @@
           <t>Nos hace entender lo difícil con mucha facilidad.</t>
         </is>
       </c>
-      <c r="E110" s="7" t="n"/>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F110" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
     </row>
-    <row r="111">
+    <row r="111" ht="43.2" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3492,7 +4060,11 @@
           <t>Es experimentado, pero es un perdedor. Además es una persona habladora. No tiene ninguna simpatía por los estudiantes hombres, pero tiene predilección por las estudiantes mujeres.</t>
         </is>
       </c>
-      <c r="E111" s="7" t="n"/>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F111" s="7" t="n">
         <v>0</v>
       </c>
@@ -3518,7 +4090,11 @@
           <t>profesor muy honorable, amable y de trato suave.</t>
         </is>
       </c>
-      <c r="E112" s="7" t="n"/>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F112" s="7" t="n">
         <v>0</v>
       </c>
@@ -3544,11 +4120,19 @@
           <t>considérenos, por favor.</t>
         </is>
       </c>
-      <c r="E113" s="7" t="n"/>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H113" s="7" t="n"/>
     </row>
     <row r="114">
@@ -3570,14 +4154,18 @@
           <t>Me cae bien porque enseña bien el laboratorio y da buenas clases.</t>
         </is>
       </c>
-      <c r="E114" s="7" t="n"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F114" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
     </row>
-    <row r="115">
+    <row r="115" ht="28.8" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3596,7 +4184,11 @@
           <t>creo que no es tan bueno como se suponía que sería y espero que lo haga mejor la próxima vez.</t>
         </is>
       </c>
-      <c r="E115" s="7" t="n"/>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F115" s="7" t="n">
         <v>0</v>
       </c>
@@ -3622,7 +4214,11 @@
           <t>Profesor veterano y constante.</t>
         </is>
       </c>
-      <c r="E116" s="7" t="n"/>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F116" s="7" t="n">
         <v>0</v>
       </c>
@@ -3648,7 +4244,11 @@
           <t>Responsable.</t>
         </is>
       </c>
-      <c r="E117" s="7" t="n"/>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F117" s="7" t="n">
         <v>0</v>
       </c>
@@ -3674,11 +4274,19 @@
           <t>Necesita mejorar.</t>
         </is>
       </c>
-      <c r="E118" s="7" t="n"/>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F118" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H118" s="7" t="n"/>
     </row>
     <row r="119">
@@ -3700,7 +4308,11 @@
           <t>Es buena</t>
         </is>
       </c>
-      <c r="E119" s="7" t="n"/>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F119" s="7" t="n">
         <v>0</v>
       </c>
@@ -3726,11 +4338,19 @@
           <t>Necesita ir un poco más despacio al dar la clase.</t>
         </is>
       </c>
-      <c r="E120" s="7" t="n"/>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F120" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H120" s="7" t="n"/>
     </row>
     <row r="121">
@@ -3752,11 +4372,19 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="E121" s="7" t="n"/>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>sin_sentido</t>
+        </is>
+      </c>
       <c r="H121" s="7" t="n"/>
     </row>
     <row r="122">
@@ -3778,14 +4406,18 @@
           <t>Buena persona y nos enseña muy bien.</t>
         </is>
       </c>
-      <c r="E122" s="7" t="n"/>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F122" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="7" t="n"/>
       <c r="H122" s="7" t="n"/>
     </row>
-    <row r="123">
+    <row r="123" ht="28.8" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3804,14 +4436,18 @@
           <t>Nuestro profesor es genial enseñando y motivando a sus estudiantes; realmente lo aprecio.</t>
         </is>
       </c>
-      <c r="E123" s="7" t="n"/>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F123" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="7" t="n"/>
       <c r="H123" s="7" t="n"/>
     </row>
-    <row r="124">
+    <row r="124" ht="28.8" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3830,14 +4466,22 @@
           <t>Es un buen profesor, pero no es atento con los estudiantes más flojos. Debería dar más tiempo a los estudiantes para entender su clase.</t>
         </is>
       </c>
-      <c r="E124" s="7" t="n"/>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F124" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H124" s="7" t="n"/>
     </row>
-    <row r="125">
+    <row r="125" ht="28.8" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3856,7 +4500,11 @@
           <t>su estilo de ensenanza es bueno. cada clase revisa, despues de ensenar, si entendimos el tema.</t>
         </is>
       </c>
-      <c r="E125" s="7" t="n"/>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F125" s="7" t="n">
         <v>0</v>
       </c>
@@ -3882,14 +4530,22 @@
           <t>¡Nadie puede preguntarle nada!</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n"/>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F126" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H126" s="7" t="n"/>
     </row>
-    <row r="127">
+    <row r="127" ht="43.2" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3908,7 +4564,11 @@
           <t>Creo que tiene un enorme conocimiento de la materia de mi curso. Su comportamiento es simplemente relajado. Esa es la clave principal de cualquier profesor. Por eso aprendimos bien.</t>
         </is>
       </c>
-      <c r="E127" s="7" t="n"/>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F127" s="7" t="n">
         <v>0</v>
       </c>
@@ -3934,7 +4594,11 @@
           <t>Es un buen profesor. Le deseo suerte.</t>
         </is>
       </c>
-      <c r="E128" s="7" t="n"/>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F128" s="7" t="n">
         <v>0</v>
       </c>
@@ -3960,14 +4624,18 @@
           <t>Los talleres son muy útiles para aprender.</t>
         </is>
       </c>
-      <c r="E129" s="7" t="n"/>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F129" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="7" t="n"/>
       <c r="H129" s="7" t="n"/>
     </row>
-    <row r="130">
+    <row r="130" ht="28.8" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -3986,11 +4654,19 @@
           <t>Bueno, debería dedicar más tiempo a ciertos puntos relacionados con la clase.</t>
         </is>
       </c>
-      <c r="E130" s="7" t="n"/>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F130" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H130" s="7" t="n"/>
     </row>
     <row r="131">
@@ -4012,11 +4688,19 @@
           <t>No está mal.</t>
         </is>
       </c>
-      <c r="E131" s="7" t="n"/>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F131" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H131" s="7" t="n"/>
     </row>
     <row r="132">
@@ -4038,7 +4722,11 @@
           <t>Puntual</t>
         </is>
       </c>
-      <c r="E132" s="7" t="n"/>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F132" s="7" t="n">
         <v>0</v>
       </c>
@@ -4064,11 +4752,19 @@
           <t>Necesita ser un poco más detallado en cuanto a la clase</t>
         </is>
       </c>
-      <c r="E133" s="7" t="n"/>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H133" s="7" t="n"/>
     </row>
     <row r="134">
@@ -4090,7 +4786,11 @@
           <t>es un buen profesor y trata de ayudar a todos los estudiantes</t>
         </is>
       </c>
-      <c r="E134" s="7" t="n"/>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F134" s="7" t="n">
         <v>0</v>
       </c>
@@ -4116,7 +4816,11 @@
           <t>Es un buen profesor.</t>
         </is>
       </c>
-      <c r="E135" s="7" t="n"/>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F135" s="7" t="n">
         <v>0</v>
       </c>
@@ -4142,7 +4846,11 @@
           <t>creo que es una buena profesora. Su método de enseñanza es bueno.</t>
         </is>
       </c>
-      <c r="E136" s="7" t="n"/>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F136" s="7" t="n">
         <v>0</v>
       </c>
@@ -4168,7 +4876,11 @@
           <t>Es una profesora muy agradable. Estamos aprendiendo algo de ella.</t>
         </is>
       </c>
-      <c r="E137" s="7" t="n"/>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F137" s="7" t="n">
         <v>0</v>
       </c>
@@ -4194,7 +4906,11 @@
           <t>Debería cambiar su actitud hacia los estudiantes.</t>
         </is>
       </c>
-      <c r="E138" s="7" t="n"/>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F138" s="7" t="n">
         <v>0</v>
       </c>
@@ -4220,14 +4936,22 @@
           <t>Puede que hayas olvidado de dónde te graduaste.</t>
         </is>
       </c>
-      <c r="E139" s="7" t="n"/>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F139" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H139" s="7" t="n"/>
     </row>
-    <row r="140">
+    <row r="140" ht="28.8" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4246,14 +4970,18 @@
           <t>Es un gran profesor. Su desempeño es excelente. Nos enseña muy muy bien. En general es el mejor profesor.</t>
         </is>
       </c>
-      <c r="E140" s="7" t="n"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F140" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G140" s="7" t="n"/>
       <c r="H140" s="7" t="n"/>
     </row>
-    <row r="141">
+    <row r="141" ht="28.8" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4272,7 +5000,11 @@
           <t>creo que debería ser más flexible y averiguar qué tipo de problemas enfrentan los estudiantes.</t>
         </is>
       </c>
-      <c r="E141" s="7" t="n"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="n">
         <v>0</v>
       </c>
@@ -4298,14 +5030,22 @@
           <t>Más o menos.</t>
         </is>
       </c>
-      <c r="E142" s="7" t="n"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F142" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H142" s="7" t="n"/>
     </row>
-    <row r="143">
+    <row r="143" ht="43.2" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4324,14 +5064,22 @@
           <t>Bueno, pero necesita cuestionarios como el quiz 3. Debe tener más cuidado al hablar. Necesita más práctica en redes de computadoras. Esta materia es aburrida, hay que hacer la lección interesante.</t>
         </is>
       </c>
-      <c r="E143" s="7" t="n"/>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F143" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H143" s="7" t="n"/>
     </row>
-    <row r="144">
+    <row r="144" ht="28.8" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4350,14 +5098,18 @@
           <t>Debería tratar de ser más claro con la materia; simplemente avanza rápido, sin considerar si lo estamos siguiendo o no.</t>
         </is>
       </c>
-      <c r="E144" s="7" t="n"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F144" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G144" s="7" t="n"/>
       <c r="H144" s="7" t="n"/>
     </row>
-    <row r="145">
+    <row r="145" ht="28.8" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4376,14 +5128,22 @@
           <t>Sí, el estilo de enseñanza es bastante bueno y favorable. Debería desarrollarse más la interacción.</t>
         </is>
       </c>
-      <c r="E145" s="7" t="n"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F145" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H145" s="7" t="n"/>
     </row>
-    <row r="146">
+    <row r="146" ht="43.2" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4402,14 +5162,18 @@
           <t>Tiene conocimientos y experiencia excepcionales sobre arquitectura. Ilustra con ejemplos. Como profesor, es muy franco y abierto con los estudiantes.</t>
         </is>
       </c>
-      <c r="E146" s="7" t="n"/>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F146" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
     </row>
-    <row r="147">
+    <row r="147" ht="28.8" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4428,7 +5192,11 @@
           <t>Básicamente es agradable. Pero es demasiado estricto durante los exámenes. Y a veces es parcial con algunos estudiantes.</t>
         </is>
       </c>
-      <c r="E147" s="7" t="n"/>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F147" s="7" t="n">
         <v>0</v>
       </c>
@@ -4454,7 +5222,11 @@
           <t>No tiene mucha idea sobre IA.</t>
         </is>
       </c>
-      <c r="E148" s="7" t="n"/>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F148" s="7" t="n">
         <v>0</v>
       </c>
@@ -4480,14 +5252,22 @@
           <t>Creo que es un profesor de nivel promedio.</t>
         </is>
       </c>
-      <c r="E149" s="7" t="n"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F149" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H149" s="7" t="n"/>
     </row>
-    <row r="150">
+    <row r="150" ht="28.8" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4506,7 +5286,11 @@
           <t>Habla demasiado de temas que no tienen relación con el estudio de la geografía económica.</t>
         </is>
       </c>
-      <c r="E150" s="7" t="n"/>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F150" s="7" t="n">
         <v>0</v>
       </c>
@@ -4532,14 +5316,18 @@
           <t>creo que es realmente perfecto para dictar el laboratorio de a.c</t>
         </is>
       </c>
-      <c r="E151" s="7" t="n"/>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F151" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G151" s="7" t="n"/>
       <c r="H151" s="7" t="n"/>
     </row>
-    <row r="152">
+    <row r="152" ht="28.8" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4558,14 +5346,18 @@
           <t>Islam, M.M. Obaidul es eficaz, calificado, cooperativo y muy cercano a nosotros.</t>
         </is>
       </c>
-      <c r="E152" s="7" t="n"/>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="n"/>
     </row>
-    <row r="153">
+    <row r="153" ht="28.8" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4584,14 +5376,18 @@
           <t>No tiene habilidad para enseñar. Solo tiene un conocimiento memorizado.</t>
         </is>
       </c>
-      <c r="E153" s="7" t="n"/>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F153" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G153" s="7" t="n"/>
       <c r="H153" s="7" t="n"/>
     </row>
-    <row r="154">
+    <row r="154" ht="28.8" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4610,11 +5406,19 @@
           <t>Esta bien, pero deberia aclarar mas sus materiales de clase, especialmente para los estudiantes de BBA.</t>
         </is>
       </c>
-      <c r="E154" s="7" t="n"/>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F154" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H154" s="7" t="n"/>
     </row>
     <row r="155">
@@ -4636,7 +5440,11 @@
           <t>El maestro más divertido y con más personalidad que he visto.</t>
         </is>
       </c>
-      <c r="E155" s="7" t="n"/>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F155" s="7" t="n">
         <v>0</v>
       </c>
@@ -4662,7 +5470,11 @@
           <t>es un excelente profesor.</t>
         </is>
       </c>
-      <c r="E156" s="7" t="n"/>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F156" s="7" t="n">
         <v>0</v>
       </c>
@@ -4688,11 +5500,19 @@
           <t>Bien, pero debería ser más amigable.</t>
         </is>
       </c>
-      <c r="E157" s="7" t="n"/>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H157" s="7" t="n"/>
     </row>
     <row r="158">
@@ -4714,11 +5534,19 @@
           <t>Es regular. Solo regular.</t>
         </is>
       </c>
-      <c r="E158" s="7" t="n"/>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F158" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H158" s="7" t="n"/>
     </row>
     <row r="159">
@@ -4740,7 +5568,11 @@
           <t>No explica bien, me siento perdido.</t>
         </is>
       </c>
-      <c r="E159" s="7" t="n"/>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F159" s="7" t="n">
         <v>0</v>
       </c>
@@ -4766,7 +5598,11 @@
           <t>La clase es muy aburrida y monótona.</t>
         </is>
       </c>
-      <c r="E160" s="7" t="n"/>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F160" s="7" t="n">
         <v>0</v>
       </c>
@@ -4792,14 +5628,22 @@
           <t>Es un robot. Pero me gusta su actitud.</t>
         </is>
       </c>
-      <c r="E161" s="7" t="n"/>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F161" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H161" s="7" t="n"/>
     </row>
-    <row r="162">
+    <row r="162" ht="28.8" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4818,7 +5662,11 @@
           <t>Para hacer entender las matemáticas de forma más fácil y sencilla, trata de poner al estudiante en la mejor posición.</t>
         </is>
       </c>
-      <c r="E162" s="7" t="n"/>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F162" s="7" t="n">
         <v>0</v>
       </c>
@@ -4844,14 +5692,18 @@
           <t>Me gusta bien su sistema de enseñanza.</t>
         </is>
       </c>
-      <c r="E163" s="7" t="n"/>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F163" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G163" s="7" t="n"/>
       <c r="H163" s="7" t="n"/>
     </row>
-    <row r="164">
+    <row r="164" ht="28.8" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4870,7 +5722,11 @@
           <t>No es adecuado para todos los tipos de estudiantes. No logró motivar a los estudiantes débiles.</t>
         </is>
       </c>
-      <c r="E164" s="7" t="n"/>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F164" s="7" t="n">
         <v>0</v>
       </c>
@@ -4896,11 +5752,19 @@
           <t>No me gusta la política de la clase.</t>
         </is>
       </c>
-      <c r="E165" s="7" t="n"/>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F165" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H165" s="7" t="n"/>
     </row>
     <row r="166">
@@ -4922,11 +5786,19 @@
           <t>Bueno, pero a veces pierde la paciencia.</t>
         </is>
       </c>
-      <c r="E166" s="7" t="n"/>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F166" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H166" s="7" t="n"/>
     </row>
     <row r="167">
@@ -4948,14 +5820,18 @@
           <t>Es extraordinario.</t>
         </is>
       </c>
-      <c r="E167" s="7" t="n"/>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F167" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G167" s="7" t="n"/>
       <c r="H167" s="7" t="n"/>
     </row>
-    <row r="168">
+    <row r="168" ht="28.8" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -4974,11 +5850,19 @@
           <t>El profesor necesita ser un poco más estricto con el ruido en clase y no debería dejar entrar tarde a los estudiantes. Es bastante distractor.</t>
         </is>
       </c>
-      <c r="E168" s="7" t="n"/>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F168" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H168" s="7" t="n"/>
     </row>
     <row r="169">
@@ -5000,11 +5884,19 @@
           <t>Buen profesor. A veces estricto, pero apropiado para algunos estudiantes.</t>
         </is>
       </c>
-      <c r="E169" s="7" t="n"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F169" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G169" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H169" s="7" t="n"/>
     </row>
     <row r="170">
@@ -5026,7 +5918,11 @@
           <t>Creo que es un buen profesor.</t>
         </is>
       </c>
-      <c r="E170" s="7" t="n"/>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F170" s="7" t="n">
         <v>0</v>
       </c>
@@ -5052,7 +5948,11 @@
           <t>Debe mejorar como profesor.</t>
         </is>
       </c>
-      <c r="E171" s="7" t="n"/>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F171" s="7" t="n">
         <v>0</v>
       </c>
@@ -5078,7 +5978,11 @@
           <t>Es un profesor excelente.</t>
         </is>
       </c>
-      <c r="E172" s="7" t="n"/>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F172" s="7" t="n">
         <v>0</v>
       </c>
@@ -5104,7 +6008,11 @@
           <t>Necesita algo de conocimiento sobre enseñanza.</t>
         </is>
       </c>
-      <c r="E173" s="7" t="n"/>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F173" s="7" t="n">
         <v>0</v>
       </c>
@@ -5130,7 +6038,11 @@
           <t>es magnífico.</t>
         </is>
       </c>
-      <c r="E174" s="7" t="n"/>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F174" s="7" t="n">
         <v>0</v>
       </c>
@@ -5156,7 +6068,11 @@
           <t>Es un buen profesor. Yo también lo apoyo.</t>
         </is>
       </c>
-      <c r="E175" s="7" t="n"/>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F175" s="7" t="n">
         <v>0</v>
       </c>
@@ -5182,7 +6098,11 @@
           <t>Debes mejorar tu conocimiento.</t>
         </is>
       </c>
-      <c r="E176" s="7" t="n"/>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F176" s="7" t="n">
         <v>0</v>
       </c>
@@ -5208,11 +6128,19 @@
           <t>Debería desempeñarse bien en los cursos superiores.</t>
         </is>
       </c>
-      <c r="E177" s="7" t="n"/>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F177" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H177" s="7" t="n"/>
     </row>
     <row r="178">
@@ -5234,11 +6162,19 @@
           <t>el material es difícil.</t>
         </is>
       </c>
-      <c r="E178" s="7" t="n"/>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F178" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>descriptivo</t>
+        </is>
+      </c>
       <c r="H178" s="7" t="n"/>
     </row>
     <row r="179">
@@ -5260,7 +6196,11 @@
           <t>Un buen profesor</t>
         </is>
       </c>
-      <c r="E179" s="7" t="n"/>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F179" s="7" t="n">
         <v>0</v>
       </c>
@@ -5286,7 +6226,11 @@
           <t>Es un muy buen profesor.</t>
         </is>
       </c>
-      <c r="E180" s="7" t="n"/>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F180" s="7" t="n">
         <v>0</v>
       </c>
@@ -5312,7 +6256,11 @@
           <t>Es un profesor con mucha experiencia y bueno.</t>
         </is>
       </c>
-      <c r="E181" s="7" t="n"/>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F181" s="7" t="n">
         <v>0</v>
       </c>
@@ -5338,14 +6286,18 @@
           <t>No es apta para aiub.</t>
         </is>
       </c>
-      <c r="E182" s="7" t="n"/>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F182" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G182" s="7" t="n"/>
       <c r="H182" s="7" t="n"/>
     </row>
-    <row r="183">
+    <row r="183" ht="28.8" customHeight="1">
       <c r="A183" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5364,14 +6316,18 @@
           <t>Necesita mucha más capacidad de comprensión y debería ser más amigable con los estudiantes. Necesita más capacidad de comprensión.</t>
         </is>
       </c>
-      <c r="E183" s="7" t="n"/>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G183" s="7" t="n"/>
       <c r="H183" s="7" t="n"/>
     </row>
-    <row r="184">
+    <row r="184" ht="28.8" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5390,14 +6346,18 @@
           <t>Buena persona con buen comportamiento, muy buen conocimiento de bases de datos y VB, con gran profundidad de conocimiento.</t>
         </is>
       </c>
-      <c r="E184" s="7" t="n"/>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F184" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="n"/>
     </row>
-    <row r="185">
+    <row r="185" ht="28.8" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5416,11 +6376,19 @@
           <t>es un buen profesor y muy divertido. lo único es que se ríe demasiado en clase.</t>
         </is>
       </c>
-      <c r="E185" s="7" t="n"/>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F185" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H185" s="7" t="n"/>
     </row>
     <row r="186">
@@ -5442,7 +6410,11 @@
           <t>En general, el profesor es bueno.</t>
         </is>
       </c>
-      <c r="E186" s="7" t="n"/>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F186" s="7" t="n">
         <v>0</v>
       </c>
@@ -5468,7 +6440,11 @@
           <t>Lo quiero y él nos quiere. El profesor Obaidul es muy buen profesor.</t>
         </is>
       </c>
-      <c r="E187" s="7" t="n"/>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F187" s="7" t="n">
         <v>0</v>
       </c>
@@ -5494,11 +6470,19 @@
           <t>Está bien.</t>
         </is>
       </c>
-      <c r="E188" s="7" t="n"/>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F188" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H188" s="7" t="n"/>
     </row>
     <row r="189">
@@ -5520,7 +6504,11 @@
           <t>Sabe muchas cosas, pero no las transmite adecuadamente.</t>
         </is>
       </c>
-      <c r="E189" s="7" t="n"/>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F189" s="7" t="n">
         <v>0</v>
       </c>
@@ -5546,14 +6534,22 @@
           <t>Desempeño promedio.</t>
         </is>
       </c>
-      <c r="E190" s="7" t="n"/>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F190" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H190" s="7" t="n"/>
     </row>
-    <row r="191">
+    <row r="191" ht="43.2" customHeight="1">
       <c r="A191" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5572,11 +6568,19 @@
           <t>Debería tener más cuidado con los estudiantes al responderles de manera correcta. Debería modificar su política de exámenes porque está muy orientada a la teoría.</t>
         </is>
       </c>
-      <c r="E191" s="7" t="n"/>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F191" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H191" s="7" t="n"/>
     </row>
     <row r="192">
@@ -5598,14 +6602,22 @@
           <t>Necesita ser un poco más detallado en cuanto a la clase</t>
         </is>
       </c>
-      <c r="E192" s="7" t="n"/>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F192" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H192" s="7" t="n"/>
     </row>
-    <row r="193">
+    <row r="193" ht="28.8" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5624,7 +6636,11 @@
           <t>entiendo la clase de la profesora, ella es capaz de aclarar nuestros conceptos sobre los temas de aprendizaje.</t>
         </is>
       </c>
-      <c r="E193" s="7" t="n"/>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F193" s="7" t="n">
         <v>0</v>
       </c>
@@ -5650,14 +6666,18 @@
           <t>Es un profesor muy agradable.</t>
         </is>
       </c>
-      <c r="E194" s="7" t="n"/>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F194" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G194" s="7" t="n"/>
       <c r="H194" s="7" t="n"/>
     </row>
-    <row r="195">
+    <row r="195" ht="28.8" customHeight="1">
       <c r="A195" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5676,14 +6696,22 @@
           <t>Bienvenido y felicidades. Espero que nos esperen mejores empleos. Buena suerte, profesor, y cuídese.</t>
         </is>
       </c>
-      <c r="E195" s="7" t="n"/>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F195" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H195" s="7" t="n"/>
     </row>
-    <row r="196">
+    <row r="196" ht="28.8" customHeight="1">
       <c r="A196" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5702,11 +6730,19 @@
           <t>es un buen profesor y un buen hombre. pero no permite que sus estudiantes se expresen.</t>
         </is>
       </c>
-      <c r="E196" s="7" t="n"/>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F196" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H196" s="7" t="n"/>
     </row>
     <row r="197">
@@ -5728,7 +6764,11 @@
           <t>es el mejor profesor.</t>
         </is>
       </c>
-      <c r="E197" s="7" t="n"/>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F197" s="7" t="n">
         <v>0</v>
       </c>
@@ -5754,7 +6794,11 @@
           <t>Trata de terminar el temario demasiado rápido.</t>
         </is>
       </c>
-      <c r="E198" s="7" t="n"/>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F198" s="7" t="n">
         <v>0</v>
       </c>
@@ -5780,7 +6824,11 @@
           <t>Es muy puntual para la clase.</t>
         </is>
       </c>
-      <c r="E199" s="7" t="n"/>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F199" s="7" t="n">
         <v>0</v>
       </c>
@@ -5806,14 +6854,18 @@
           <t>es un profesor muy honesto.</t>
         </is>
       </c>
-      <c r="E200" s="7" t="n"/>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F200" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G200" s="7" t="n"/>
       <c r="H200" s="7" t="n"/>
     </row>
-    <row r="201">
+    <row r="201" ht="57.6" customHeight="1">
       <c r="A201" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5832,14 +6884,18 @@
           <t>Quiere hacerlo mejor para ayudar a los estudiantes a mejorar su desempeño en clase y su conocimiento. Trata de identificar especialmente a los más lentos que no logran entender las materias. Por eso es un buen profesor.</t>
         </is>
       </c>
-      <c r="E201" s="7" t="n"/>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F201" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G201" s="7" t="n"/>
       <c r="H201" s="7" t="n"/>
     </row>
-    <row r="202">
+    <row r="202" ht="28.8" customHeight="1">
       <c r="A202" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5858,11 +6914,19 @@
           <t>Es nueva, así que necesita mucho más tiempo para familiarizarse con la enseñanza.</t>
         </is>
       </c>
-      <c r="E202" s="7" t="n"/>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F202" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H202" s="7" t="n"/>
     </row>
     <row r="203">
@@ -5884,11 +6948,19 @@
           <t>es un profesor maravilloso. es el mejor, pero su voz es demasiado baja.</t>
         </is>
       </c>
-      <c r="E203" s="7" t="n"/>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F203" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H203" s="7" t="n"/>
     </row>
     <row r="204">
@@ -5910,14 +6982,18 @@
           <t>Es muy buen profesor.</t>
         </is>
       </c>
-      <c r="E204" s="7" t="n"/>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F204" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G204" s="7" t="n"/>
       <c r="H204" s="7" t="n"/>
     </row>
-    <row r="205">
+    <row r="205" ht="28.8" customHeight="1">
       <c r="A205" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -5936,7 +7012,11 @@
           <t>El profesor Shafiqul es mi profesor favorito favorito. Su estilo de enseñanza es muy bueno.</t>
         </is>
       </c>
-      <c r="E205" s="7" t="n"/>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F205" s="7" t="n">
         <v>0</v>
       </c>
@@ -5962,7 +7042,11 @@
           <t>Es un profesor realmente bueno para los estudiantes.</t>
         </is>
       </c>
-      <c r="E206" s="7" t="n"/>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F206" s="7" t="n">
         <v>0</v>
       </c>
@@ -5988,14 +7072,18 @@
           <t>muy buen profesor y ante todo sincero</t>
         </is>
       </c>
-      <c r="E207" s="7" t="n"/>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F207" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G207" s="7" t="n"/>
       <c r="H207" s="7" t="n"/>
     </row>
-    <row r="208">
+    <row r="208" ht="28.8" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6014,11 +7102,19 @@
           <t>Su pronunciación tiene acento regional; a veces es difícil de entender en clase</t>
         </is>
       </c>
-      <c r="E208" s="7" t="n"/>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F208" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>critica_suave</t>
+        </is>
+      </c>
       <c r="H208" s="7" t="n"/>
     </row>
     <row r="209">
@@ -6040,7 +7136,11 @@
           <t>Disfruto mucho su clase, porque la hace amena con buenos ejemplos.</t>
         </is>
       </c>
-      <c r="E209" s="7" t="n"/>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F209" s="7" t="n">
         <v>0</v>
       </c>
@@ -6066,7 +7166,11 @@
           <t>La clase es muy dinámica y entretenida.</t>
         </is>
       </c>
-      <c r="E210" s="7" t="n"/>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F210" s="7" t="n">
         <v>0</v>
       </c>
@@ -6092,7 +7196,11 @@
           <t>Explica muy bien los temas.</t>
         </is>
       </c>
-      <c r="E211" s="7" t="n"/>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F211" s="7" t="n">
         <v>0</v>
       </c>
@@ -6118,7 +7226,11 @@
           <t>Bien. No hay ningún problema. Buen desempeño.</t>
         </is>
       </c>
-      <c r="E212" s="7" t="n"/>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F212" s="7" t="n">
         <v>0</v>
       </c>
@@ -6144,7 +7256,11 @@
           <t>Es genial.</t>
         </is>
       </c>
-      <c r="E213" s="7" t="n"/>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F213" s="7" t="n">
         <v>0</v>
       </c>
@@ -6170,7 +7286,11 @@
           <t>profesor brillante</t>
         </is>
       </c>
-      <c r="E214" s="7" t="n"/>
+      <c r="E214" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F214" s="7" t="n">
         <v>0</v>
       </c>
@@ -6196,14 +7316,22 @@
           <t>Profesor.</t>
         </is>
       </c>
-      <c r="E215" s="7" t="n"/>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F215" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>muy_corto</t>
+        </is>
+      </c>
       <c r="H215" s="7" t="n"/>
     </row>
-    <row r="216">
+    <row r="216" ht="28.8" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6222,11 +7350,19 @@
           <t>El Sr. Mujibur Rahman es un buen profesor, aunque los estudiantes más lentos podrían encontrarlo un poco demasiado rápido.</t>
         </is>
       </c>
-      <c r="E216" s="7" t="n"/>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F216" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H216" s="7" t="n"/>
     </row>
     <row r="217">
@@ -6248,14 +7384,22 @@
           <t>Excelente, pero pone preguntas difíciles.</t>
         </is>
       </c>
-      <c r="E217" s="7" t="n"/>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F217" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H217" s="7" t="n"/>
     </row>
-    <row r="218">
+    <row r="218" ht="28.8" customHeight="1">
       <c r="A218" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6274,7 +7418,11 @@
           <t>Es una profesora agradable y tiene un buen método para hacer que la clase se entienda.</t>
         </is>
       </c>
-      <c r="E218" s="7" t="n"/>
+      <c r="E218" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F218" s="7" t="n">
         <v>0</v>
       </c>
@@ -6300,11 +7448,19 @@
           <t>Es un buen profesor, pero a veces es tan rápido que no se le entiende.</t>
         </is>
       </c>
-      <c r="E219" s="7" t="n"/>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F219" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H219" s="7" t="n"/>
     </row>
     <row r="220">
@@ -6326,14 +7482,18 @@
           <t>Califica de forma injusta.</t>
         </is>
       </c>
-      <c r="E220" s="7" t="n"/>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F220" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G220" s="7" t="n"/>
       <c r="H220" s="7" t="n"/>
     </row>
-    <row r="221">
+    <row r="221" ht="28.8" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6352,14 +7512,18 @@
           <t>A veces él mismo no tiene claro lo que está enseñando. Para mí no es suficientemente bueno.</t>
         </is>
       </c>
-      <c r="E221" s="7" t="n"/>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F221" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G221" s="7" t="n"/>
       <c r="H221" s="7" t="n"/>
     </row>
-    <row r="222">
+    <row r="222" ht="43.2" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6378,11 +7542,19 @@
           <t>Es un profesor excelente, pero su método de enseñanza es muy difícil. Por ejemplo, su sistema de exámenes sorpresa a menudo perjudica nuestra calificación.</t>
         </is>
       </c>
-      <c r="E222" s="7" t="n"/>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F222" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H222" s="7" t="n"/>
     </row>
     <row r="223">
@@ -6404,7 +7576,11 @@
           <t>Excelente profesor, muy claro.</t>
         </is>
       </c>
-      <c r="E223" s="7" t="n"/>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F223" s="7" t="n">
         <v>0</v>
       </c>
@@ -6430,14 +7606,18 @@
           <t>Es un buen profesor. Creo que AIUB necesita este tipo de profesores.</t>
         </is>
       </c>
-      <c r="E224" s="7" t="n"/>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F224" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="7" t="n"/>
       <c r="H224" s="7" t="n"/>
     </row>
-    <row r="225">
+    <row r="225" ht="28.8" customHeight="1">
       <c r="A225" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6456,14 +7636,22 @@
           <t>En general, es un buen profesor y estaríamos más contentos si diera ejemplos y casos más realistas</t>
         </is>
       </c>
-      <c r="E225" s="7" t="n"/>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F225" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H225" s="7" t="n"/>
     </row>
-    <row r="226">
+    <row r="226" ht="28.8" customHeight="1">
       <c r="A226" s="5" t="inlineStr">
         <is>
           <t>A3</t>
@@ -6482,7 +7670,11 @@
           <t>Su estilo de enseñanza no es muy bueno y los estudiantes no sienten interés por esta materia.</t>
         </is>
       </c>
-      <c r="E226" s="7" t="n"/>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F226" s="7" t="n">
         <v>0</v>
       </c>
@@ -6508,7 +7700,11 @@
           <t>Tiene buen dominio.</t>
         </is>
       </c>
-      <c r="E227" s="7" t="n"/>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F227" s="7" t="n">
         <v>0</v>
       </c>
@@ -6522,45 +7718,57 @@
         </is>
       </c>
       <c r="B228" s="5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>A3-76B92E</t>
+          <t>A3-73B8ED</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>gseb ndfg</t>
-        </is>
-      </c>
-      <c r="E228" s="7" t="n"/>
+          <t>si los estudiantes pudieran ver su examen de cuestionario y de parcial, entonces podrían entender sus errores y hacerlo bien en el final.</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F228" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>otro</t>
+        </is>
+      </c>
       <c r="H228" s="7" t="n"/>
     </row>
-    <row r="229">
+    <row r="229" ht="28.8" customHeight="1">
       <c r="A229" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B229" s="5" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>A3-73B8ED</t>
+          <t>A3-652BD7</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>si los estudiantes pudieran ver su examen de cuestionario y de parcial, entonces podrían entender sus errores y hacerlo bien en el final.</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="n"/>
+          <t>Es una buena persona.</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F229" s="7" t="n">
         <v>0</v>
       </c>
@@ -6574,19 +7782,23 @@
         </is>
       </c>
       <c r="B230" s="5" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>A3-652BD7</t>
+          <t>A3-B07201</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>Es una buena persona.</t>
-        </is>
-      </c>
-      <c r="E230" s="7" t="n"/>
+          <t>Debe mejorar como profesor.</t>
+        </is>
+      </c>
+      <c r="E230" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F230" s="7" t="n">
         <v>0</v>
       </c>
@@ -6600,19 +7812,23 @@
         </is>
       </c>
       <c r="B231" s="5" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>A3-B07201</t>
+          <t>A3-3E2440</t>
         </is>
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>Debe mejorar como profesor.</t>
-        </is>
-      </c>
-      <c r="E231" s="7" t="n"/>
+          <t>es un buen profesor y es muy servicial.</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F231" s="7" t="n">
         <v>0</v>
       </c>
@@ -6626,19 +7842,23 @@
         </is>
       </c>
       <c r="B232" s="5" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>A3-3E2440</t>
+          <t>A3-BA47D6</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>es un buen profesor y es muy servicial.</t>
-        </is>
-      </c>
-      <c r="E232" s="7" t="n"/>
+          <t>Siempre esta bien preparado.</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F232" s="7" t="n">
         <v>0</v>
       </c>
@@ -6652,19 +7872,23 @@
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>A3-BA47D6</t>
+          <t>A3-B361FC</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>Siempre esta bien preparado.</t>
-        </is>
-      </c>
-      <c r="E233" s="7" t="n"/>
+          <t>Es muy alentador.</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F233" s="7" t="n">
         <v>0</v>
       </c>
@@ -6678,23 +7902,31 @@
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>A3-B361FC</t>
+          <t>A3-52B378</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>Es muy alentador.</t>
-        </is>
-      </c>
-      <c r="E234" s="7" t="n"/>
+          <t>Su estilo de enseñanza es de nivel B+.</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F234" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H234" s="7" t="n"/>
     </row>
     <row r="235">
@@ -6704,19 +7936,23 @@
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>A3-52B378</t>
+          <t>A3-CDC920</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>Su estilo de enseñanza es de nivel B+.</t>
-        </is>
-      </c>
-      <c r="E235" s="7" t="n"/>
+          <t>Es cooperativa</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F235" s="7" t="n">
         <v>0</v>
       </c>
@@ -6730,45 +7966,57 @@
         </is>
       </c>
       <c r="B236" s="5" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>A3-CDC920</t>
+          <t>A3-F86948</t>
         </is>
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>Es cooperativa</t>
-        </is>
-      </c>
-      <c r="E236" s="7" t="n"/>
+          <t>Es un muy buen profesor, pero a veces te tomas demasiado en serio cosas simples.</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F236" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H236" s="7" t="n"/>
     </row>
-    <row r="237">
+    <row r="237" ht="28.8" customHeight="1">
       <c r="A237" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>A3-F86948</t>
+          <t>A3-60C52C</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>Es un muy buen profesor, pero a veces te tomas demasiado en serio cosas simples.</t>
-        </is>
-      </c>
-      <c r="E237" s="7" t="n"/>
+          <t>Es un profesor brillante y talentoso. Su comportamiento es muy bueno.</t>
+        </is>
+      </c>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F237" s="7" t="n">
         <v>0</v>
       </c>
@@ -6782,49 +8030,61 @@
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>A3-60C52C</t>
+          <t>A3-F05EB9</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>Es un profesor brillante y talentoso. Su comportamiento es muy bueno.</t>
-        </is>
-      </c>
-      <c r="E238" s="7" t="n"/>
+          <t>Estoy orgulloso de ser estudiante de este profesor. Creo que Ghani, Md. Bayzid es un buen profesor por su buena enseñanza, comprensión, buen desempeño docente y buen comportamiento.</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F238" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G238" s="7" t="n"/>
       <c r="H238" s="7" t="n"/>
     </row>
-    <row r="239">
+    <row r="239" ht="43.2" customHeight="1">
       <c r="A239" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>A3-F05EB9</t>
+          <t>A3-272FE2</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>Estoy orgulloso de ser estudiante de este profesor. Creo que Ghani, Md. Bayzid es un buen profesor por su buena enseñanza, comprensión, buen desempeño docente y buen comportamiento.</t>
-        </is>
-      </c>
-      <c r="E239" s="7" t="n"/>
+          <t>Es duro pero buen profesor.</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F239" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H239" s="7" t="n"/>
     </row>
     <row r="240">
@@ -6834,45 +8094,53 @@
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>A3-272FE2</t>
+          <t>A3-B6DCCE</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>Es duro pero buen profesor.</t>
-        </is>
-      </c>
-      <c r="E240" s="7" t="n"/>
+          <t>Es uno de los mejores profesores de aiub. Tiene muchos conocimientos y sabe cómo hacer que sus estudiantes aprendan más que solo los materiales de estudio.</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F240" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G240" s="7" t="n"/>
       <c r="H240" s="7" t="n"/>
     </row>
-    <row r="241">
+    <row r="241" ht="43.2" customHeight="1">
       <c r="A241" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>A3-B6DCCE</t>
+          <t>A3-41CA0F</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>Es uno de los mejores profesores de aiub. Tiene muchos conocimientos y sabe cómo hacer que sus estudiantes aprendan más que solo los materiales de estudio.</t>
-        </is>
-      </c>
-      <c r="E241" s="7" t="n"/>
+          <t>Muy mal profesor.</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F241" s="7" t="n">
         <v>0</v>
       </c>
@@ -6886,19 +8154,23 @@
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>A3-41CA0F</t>
+          <t>A3-0FF2C4</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>Muy mal profesor.</t>
-        </is>
-      </c>
-      <c r="E242" s="7" t="n"/>
+          <t>Muy listo</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F242" s="7" t="n">
         <v>0</v>
       </c>
@@ -6912,49 +8184,61 @@
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>A3-0FF2C4</t>
+          <t>A3-E97E2F</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>Muy listo</t>
-        </is>
-      </c>
-      <c r="E243" s="7" t="n"/>
+          <t>desde mi perspectiva, es una de las mejores profesoras de aiub. Hay algunas razones. Una es que revisa a todos y cada uno de los estudiantes para ver si entienden o no.</t>
+        </is>
+      </c>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F243" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G243" s="7" t="n"/>
       <c r="H243" s="7" t="n"/>
     </row>
-    <row r="244">
+    <row r="244" ht="43.2" customHeight="1">
       <c r="A244" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B244" s="5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>A3-E97E2F</t>
+          <t>A3-131A7A</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>desde mi perspectiva, es una de las mejores profesoras de aiub. Hay algunas razones. Una es que revisa a todos y cada uno de los estudiantes para ver si entienden o no.</t>
-        </is>
-      </c>
-      <c r="E244" s="7" t="n"/>
+          <t>Está bien, pero no excepcional.</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>NEU</t>
+        </is>
+      </c>
       <c r="F244" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>elogio_tibio</t>
+        </is>
+      </c>
       <c r="H244" s="7" t="n"/>
     </row>
     <row r="245">
@@ -6964,19 +8248,23 @@
         </is>
       </c>
       <c r="B245" s="5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>A3-131A7A</t>
+          <t>A3-D5DA7F</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>Está bien, pero no excepcional.</t>
-        </is>
-      </c>
-      <c r="E245" s="7" t="n"/>
+          <t>Gran profesor</t>
+        </is>
+      </c>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F245" s="7" t="n">
         <v>0</v>
       </c>
@@ -6990,71 +8278,83 @@
         </is>
       </c>
       <c r="B246" s="5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>A3-D5DA7F</t>
+          <t>A3-6B9C91</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>Gran profesor</t>
-        </is>
-      </c>
-      <c r="E246" s="7" t="n"/>
+          <t>Uno de mis profesores favoritos. Me gusta asistir a cada una de sus clases. Me gusta su método de enseñanza. Especialmente me gustan los trabajos en grupo que nos da en clase y que de verdad nos ayudan.</t>
+        </is>
+      </c>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F246" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G246" s="7" t="n"/>
       <c r="H246" s="7" t="n"/>
     </row>
-    <row r="247">
+    <row r="247" ht="43.2" customHeight="1">
       <c r="A247" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B247" s="5" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>A3-6B9C91</t>
+          <t>A3-6C6918</t>
         </is>
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>Uno de mis profesores favoritos. Me gusta asistir a cada una de sus clases. Me gusta su método de enseñanza. Especialmente me gustan los trabajos en grupo que nos da en clase y que de verdad nos ayudan.</t>
-        </is>
-      </c>
-      <c r="E247" s="7" t="n"/>
+          <t>Es un profesor excelente. Espero que la universidad lo trate como corresponde.</t>
+        </is>
+      </c>
+      <c r="E247" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F247" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G247" s="7" t="n"/>
       <c r="H247" s="7" t="n"/>
     </row>
-    <row r="248">
+    <row r="248" ht="28.8" customHeight="1">
       <c r="A248" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>A3-6C6918</t>
+          <t>A3-F166B5</t>
         </is>
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>Es un profesor excelente. Espero que la universidad lo trate como corresponde.</t>
-        </is>
-      </c>
-      <c r="E248" s="7" t="n"/>
+          <t>muy buen profesor</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F248" s="7" t="n">
         <v>0</v>
       </c>
@@ -7068,45 +8368,57 @@
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>A3-F166B5</t>
+          <t>A3-C5D6AC</t>
         </is>
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>muy buen profesor</t>
-        </is>
-      </c>
-      <c r="E249" s="7" t="n"/>
+          <t>Es un buen profesor. Como estudiante de MBA, espero un comportamiento más profesional.</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F249" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G249" s="7" t="inlineStr">
+        <is>
+          <t>mixto_adversativa</t>
+        </is>
+      </c>
       <c r="H249" s="7" t="n"/>
     </row>
-    <row r="250">
+    <row r="250" ht="28.8" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>A3-C5D6AC</t>
+          <t>A3-D40943</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>Es un buen profesor. Como estudiante de MBA, espero un comportamiento más profesional.</t>
-        </is>
-      </c>
-      <c r="E250" s="7" t="n"/>
+          <t>siempre miente sobre su posición</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
       <c r="F250" s="7" t="n">
         <v>0</v>
       </c>
@@ -7120,51 +8432,30 @@
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>A3-D40943</t>
+          <t>A3-F88664</t>
         </is>
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>siempre miente sobre su posición</t>
-        </is>
-      </c>
-      <c r="E251" s="7" t="n"/>
+          <t>Es muy bueno en diseño de compiladores. Creo que es uno de los mejores en este curso</t>
+        </is>
+      </c>
+      <c r="E251" s="7" t="inlineStr">
+        <is>
+          <t>POS</t>
+        </is>
+      </c>
       <c r="F251" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G251" s="7" t="n"/>
       <c r="H251" s="7" t="n"/>
     </row>
-    <row r="252">
-      <c r="A252" s="5" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B252" s="5" t="n">
-        <v>251</v>
-      </c>
-      <c r="C252" s="5" t="inlineStr">
-        <is>
-          <t>A3-F88664</t>
-        </is>
-      </c>
-      <c r="D252" s="6" t="inlineStr">
-        <is>
-          <t>Es muy bueno en diseño de compiladores. Creo que es uno de los mejores en este curso</t>
-        </is>
-      </c>
-      <c r="E252" s="7" t="n"/>
-      <c r="F252" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" s="7" t="n"/>
-      <c r="H252" s="7" t="n"/>
-    </row>
+    <row r="252" ht="28.8" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="0" password="8AE1"/>
   <dataValidations count="3">
